--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des tailles différentes. Josette va vers Wilfried. Elle dit : tu veux jouer ? Wilfried dit : oui. Ils jouent ensemble. Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux. Maman dit : petit ou grand, on peut jouer ensemble. Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
+          <t>Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des tailles différentes. Josette va vers Wilfried. Tu veux jouer ? Oui. Ils jouent ensemble. Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux. Petit ou grand, on peut jouer ensemble. Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des tailles différentes. Josette va vers Wilfried.
+narrateur|Tu veux jouer ?
+copain|Oui. Ils jouent ensemble.
+narrateur|Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux.
+maman|Petit ou grand, on peut jouer ensemble.
+narrateur|Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Josette invite Wilfried. Que font-ils ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Josette a invité. Wilfried a dit oui. Ils ont des tailles différentes. Ils jouent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1657,7 +1693,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman dit : on rentre. Josette range un cerceau. Wilfried range l'autre.</t>
+          <t>On rentre. Josette range un cerceau. Wilfried range l'autre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1791,6 +1827,12 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>maman|On rentre.
+narrateur|Josette range un cerceau. Wilfried range l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Josette invite Wilfried. Que font-ils ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Josette a invité. Wilfried a dit oui. Ils ont des tailles différentes. Ils jouent ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
 narrateur|Josette range un cerceau. Wilfried range l'autre.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Josette et Wilfried jouent ensemble</t>
+          <t>La marelle bleue de la cour</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une marelle bleue attend dans la cour. Sarah invite Victorino. Ils ont des tailles différentes. Ils roulent les cerceaux ensemble.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des tailles différentes. Josette va vers Wilfried. Tu veux jouer ? Oui. Ils jouent ensemble. Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux. Petit ou grand, on peut jouer ensemble. Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
+          <t>La cloche a déjà sonné. Elle sonne encore, loin. Les pierres de la cour sont fraîches. Une marelle bleue attend au sol. La craie colle un peu aux doigts. Un moineau saute près du caniveau. Le foulard de maman bouge au portail. En ce moment, Sarah est dans la cour. Tu vois la marelle, Sarah ? Oui. Elle est bleue. Sarah pose le pied sur un carré. Le carré est un peu poudreux. Victorino arrive. Il tient un grand cerceau. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux jouer ? Oui. Ils jouent ensemble. Sarah a un petit cerceau. Victorino a un grand cerceau. On joue. On reste gentils. Ils roulent les cerceaux. Le petit cerceau va vite. Le grand cerceau va loin. Les cerceaux font un bruit doux. Petit ou grand, on peut jouer ensemble. Encore ! Encore. Sarah relance le petit cerceau. Victorino relance le grand. Ils rient du jeu. La marelle bleue reste au sol. Vous jouez ensemble. Bravo. Vous avez des tailles différentes. Et vous jouez ensemble. Sarah saute un carré bleu. Victorino saute le carré d'après. La craie est douce, hein ? Oui. Elle est douce. Le moineau s'envole un peu. Puis il revient.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des tailles différentes. Josette va vers Wilfried.
-narrateur|Tu veux jouer ?
-copain|Oui. Ils jouent ensemble.
-narrateur|Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux.
+          <t>narrateur|La cloche a déjà sonné.
+narrateur|Elle sonne encore, loin.
+narrateur|Les pierres de la cour sont fraîches.
+narrateur|Une marelle bleue attend au sol.
+narrateur|La craie colle un peu aux doigts.
+narrateur|Un moineau saute près du caniveau.
+narrateur|Le foulard de maman bouge au portail.
+narrateur|En ce moment, Sarah est dans la cour.
+maman|Tu vois la marelle, Sarah ?
+enfant-f|Oui. Elle est bleue.
+narrateur|Sarah pose le pied sur un carré.
+narrateur|Le carré est un peu poudreux.
+narrateur|Victorino arrive.
+narrateur|Il tient un grand cerceau.
+narrateur|Victorino est plus grand.
+narrateur|Sarah est plus petite.
+narrateur|Ils ont des tailles différentes.
+maman|Victorino est là. Tu l'invites ?
+enfant-f|Tu veux jouer ?
+copain|Oui.
+narrateur|Ils jouent ensemble.
+narrateur|Sarah a un petit cerceau.
+narrateur|Victorino a un grand cerceau.
+maman|On joue. On reste gentils.
+narrateur|Ils roulent les cerceaux.
+narrateur|Le petit cerceau va vite.
+narrateur|Le grand cerceau va loin.
+narrateur|Les cerceaux font un bruit doux.
 maman|Petit ou grand, on peut jouer ensemble.
-narrateur|Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.</t>
+enfant-f|Encore !
+copain|Encore.
+narrateur|Sarah relance le petit cerceau.
+narrateur|Victorino relance le grand.
+narrateur|Ils rient du jeu.
+narrateur|La marelle bleue reste au sol.
+maman|Vous jouez ensemble. Bravo.
+maman|Vous avez des tailles différentes.
+maman|Et vous jouez ensemble.
+narrateur|Sarah saute un carré bleu.
+narrateur|Victorino saute le carré d'après.
+maman|La craie est douce, hein ?
+enfant-f|Oui. Elle est douce.
+narrateur|Le moineau s'envole un peu.
+narrateur|Puis il revient.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1395,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Josette invite Wilfried. Que font-ils ?</t>
+          <t>Sarah invite Victorino. Que font-ils ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1551,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Josette invite Wilfried. Que font-ils ?</t>
+          <t>narrateur|Sarah invite Victorino.
+narrateur|Que font-ils ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1580,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Josette a invité. Wilfried a dit oui. Ils ont des tailles différentes. Ils jouent ensemble.</t>
+          <t>Sarah a invité. Victorino a dit oui. Ils ont des tailles différentes. Ils jouent ensemble. Bravo, Sarah. Tu as fait du bon travail. Vous roulez les cerceaux. Sarah tient encore le petit cerceau. Victorino tient le grand. Le mien est petit. Le mien est grand. Et vous jouez ensemble. C'est ça. Ils roulent encore une fois. Les cerceaux s'arrêtent près de la marelle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,7 +1724,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Josette a invité. Wilfried a dit oui. Ils ont des tailles différentes. Ils jouent ensemble.</t>
+          <t>narrateur|Sarah a invité.
+narrateur|Victorino a dit oui.
+narrateur|Ils ont des tailles différentes.
+narrateur|Ils jouent ensemble.
+maman|Bravo, Sarah. Tu as fait du bon travail.
+maman|Vous roulez les cerceaux.
+narrateur|Sarah tient encore le petit cerceau.
+narrateur|Victorino tient le grand.
+enfant-f|Le mien est petit.
+copain|Le mien est grand.
+maman|Et vous jouez ensemble. C'est ça.
+narrateur|Ils roulent encore une fois.
+narrateur|Les cerceaux s'arrêtent près de la marelle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1764,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On rentre. Josette range un cerceau. Wilfried range l'autre.</t>
+          <t>On rentre. Sarah range un cerceau. Victorino range l'autre. Tu as fini de ranger le cerceau ? Oui, maman. Merci. Bravo. Sarah regarde la marelle bleue. La craie brille un peu. Au revoir, marelle. On revient un autre jour. Le foulard de maman bouge encore. Les pierres de la cour restent fraîches.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1901,17 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>maman|On rentre.
-narrateur|Josette range un cerceau. Wilfried range l'autre.</t>
+narrateur|Sarah range un cerceau.
+narrateur|Victorino range l'autre.
+maman|Tu as fini de ranger le cerceau ?
+enfant-f|Oui, maman.
+maman|Merci. Bravo.
+narrateur|Sarah regarde la marelle bleue.
+narrateur|La craie brille un peu.
+enfant-f|Au revoir, marelle.
+maman|On revient un autre jour.
+narrateur|Le foulard de maman bouge encore.
+narrateur|Les pierres de la cour restent fraîches.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1939,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a joué ensemble. Petit ou grand, on peut jouer ensemble. Bravo. C'était du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2079,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|On a joué ensemble.
+maman|Petit ou grand, on peut jouer ensemble.
+maman|Bravo. C'était du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2142,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La cloche a déjà sonné. Elle sonne encore, loin. Les pierres de la cour sont fraîches. Une marelle bleue attend au sol. La craie colle un peu aux doigts. Un moineau saute près du caniveau. Le foulard de maman bouge au portail. En ce moment, Sarah est dans la cour. Tu vois la marelle, Sarah ? Oui. Elle est bleue. Sarah pose le pied sur un carré. Le carré est un peu poudreux. Victorino arrive. Il tient un grand cerceau. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux jouer ? Oui. Ils jouent ensemble. Sarah a un petit cerceau. Victorino a un grand cerceau. On joue. On reste gentils. Ils roulent les cerceaux. Le petit cerceau va vite. Le grand cerceau va loin. Les cerceaux font un bruit doux. Petit ou grand, on peut jouer ensemble. Encore ! Encore. Sarah relance le petit cerceau. Victorino relance le grand. Ils rient du jeu. La marelle bleue reste au sol. Vous jouez ensemble. Bravo. Vous avez des tailles différentes. Et vous jouez ensemble. Sarah saute un carré bleu. Victorino saute le carré d'après. La craie est douce, hein ? Oui. Elle est douce. Le moineau s'envole un peu. Puis il revient.</t>
+          <t>La cloche a déjà sonné. Elle sonne encore, loin. Les pierres de la cour sont fraîches. Une marelle bleue attend au sol. La craie colle un peu aux doigts. Un moineau saute près du caniveau. Le foulard de maman bouge au portail. En ce moment, Sarah est dans la cour. Tu vois la marelle, Sarah ? Oui. Elle est bleue. Sarah pose le pied sur un carré. Le carré est un peu poudreux. Victorino arrive. Il tient un grand cerceau. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux jouer ? Oui. Ils jouent ensemble. Sarah a un petit cerceau. Victorino a un grand cerceau. On joue. On reste gentils. Ils roulent les cerceaux. Le petit cerceau va vite. Le grand cerceau va loin. Les cerceaux font un bruit doux. Petit ou grand, on peut jouer ensemble. Encore ! Encore. Sarah relance le petit cerceau. Victorino relance le grand. Ils rient du jeu. La marelle bleue reste au sol. Vous jouez ensemble. Bravo. Vous avez des tailles différentes. Et vous jouez ensemble. Sarah saute un carré bleu. Victorino saute le carré d'après. La craie est douce, hein ? Oui. Elle est douce. Le moineau s'envole un peu. Puis il revient. Sarah souffle sur la craie. Un peu de bleu s'envole. Victorino souffle aussi. La poussière brille au soleil. Elle brille. Sarah pose le petit cerceau sur un carré. Victorino pose le grand à côté. Les deux cerceaux se touchent. Petit cerceau. Grand cerceau. Ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1333,7 +1333,8 @@
 narrateur|Le foulard de maman bouge au portail.
 narrateur|En ce moment, Sarah est dans la cour.
 maman|Tu vois la marelle, Sarah ?
-enfant-f|Oui. Elle est bleue.
+enfant-f|Oui.
+enfant-f|Elle est bleue.
 narrateur|Sarah pose le pied sur un carré.
 narrateur|Le carré est un peu poudreux.
 narrateur|Victorino arrive.
@@ -1341,13 +1342,15 @@
 narrateur|Victorino est plus grand.
 narrateur|Sarah est plus petite.
 narrateur|Ils ont des tailles différentes.
-maman|Victorino est là. Tu l'invites ?
+maman|Victorino est là.
+maman|Tu l'invites ?
 enfant-f|Tu veux jouer ?
 copain|Oui.
 narrateur|Ils jouent ensemble.
 narrateur|Sarah a un petit cerceau.
 narrateur|Victorino a un grand cerceau.
-maman|On joue. On reste gentils.
+maman|On joue.
+maman|On reste gentils.
 narrateur|Ils roulent les cerceaux.
 narrateur|Le petit cerceau va vite.
 narrateur|Le grand cerceau va loin.
@@ -1359,15 +1362,28 @@
 narrateur|Victorino relance le grand.
 narrateur|Ils rient du jeu.
 narrateur|La marelle bleue reste au sol.
-maman|Vous jouez ensemble. Bravo.
+maman|Vous jouez ensemble.
+maman|Bravo.
 maman|Vous avez des tailles différentes.
 maman|Et vous jouez ensemble.
 narrateur|Sarah saute un carré bleu.
 narrateur|Victorino saute le carré d'après.
 maman|La craie est douce, hein ?
-enfant-f|Oui. Elle est douce.
+enfant-f|Oui.
+enfant-f|Elle est douce.
 narrateur|Le moineau s'envole un peu.
-narrateur|Puis il revient.</t>
+narrateur|Puis il revient.
+narrateur|Sarah souffle sur la craie.
+narrateur|Un peu de bleu s'envole.
+narrateur|Victorino souffle aussi.
+maman|La poussière brille au soleil.
+enfant-f|Elle brille.
+narrateur|Sarah pose le petit cerceau sur un carré.
+narrateur|Victorino pose le grand à côté.
+narrateur|Les deux cerceaux se touchent.
+maman|Petit cerceau.
+maman|Grand cerceau.
+maman|Ensemble.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1728,13 +1744,15 @@
 narrateur|Victorino a dit oui.
 narrateur|Ils ont des tailles différentes.
 narrateur|Ils jouent ensemble.
-maman|Bravo, Sarah. Tu as fait du bon travail.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
 maman|Vous roulez les cerceaux.
 narrateur|Sarah tient encore le petit cerceau.
 narrateur|Victorino tient le grand.
 enfant-f|Le mien est petit.
 copain|Le mien est grand.
-maman|Et vous jouez ensemble. C'est ça.
+maman|Et vous jouez ensemble.
+maman|C'est ça.
 narrateur|Ils roulent encore une fois.
 narrateur|Les cerceaux s'arrêtent près de la marelle.</t>
         </is>
@@ -1905,7 +1923,8 @@
 narrateur|Victorino range l'autre.
 maman|Tu as fini de ranger le cerceau ?
 enfant-f|Oui, maman.
-maman|Merci. Bravo.
+maman|Merci.
+maman|Bravo.
 narrateur|Sarah regarde la marelle bleue.
 narrateur|La craie brille un peu.
 enfant-f|Au revoir, marelle.
@@ -2081,7 +2100,8 @@
         <is>
           <t>enfant-f|On a joué ensemble.
 maman|Petit ou grand, on peut jouer ensemble.
-maman|Bravo. C'était du bon travail.
+maman|Bravo.
+maman|C'était du bon travail.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2104,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2147,6 +2167,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La marelle bleue de la cour</t>
+          <t>Le train de coussins de Sarah</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une marelle bleue attend dans la cour. Sarah invite Victorino. Ils ont des tailles différentes. Ils roulent les cerceaux ensemble.</t>
+          <t>Sarah veut un train de coussins jusqu'à la porte. Un coussin est coincé. Victorino est plus grand. Sarah est plus petite. Ils vont voir la lune, ensemble.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La cloche a déjà sonné. Elle sonne encore, loin. Les pierres de la cour sont fraîches. Une marelle bleue attend au sol. La craie colle un peu aux doigts. Un moineau saute près du caniveau. Le foulard de maman bouge au portail. En ce moment, Sarah est dans la cour. Tu vois la marelle, Sarah ? Oui. Elle est bleue. Sarah pose le pied sur un carré. Le carré est un peu poudreux. Victorino arrive. Il tient un grand cerceau. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux jouer ? Oui. Ils jouent ensemble. Sarah a un petit cerceau. Victorino a un grand cerceau. On joue. On reste gentils. Ils roulent les cerceaux. Le petit cerceau va vite. Le grand cerceau va loin. Les cerceaux font un bruit doux. Petit ou grand, on peut jouer ensemble. Encore ! Encore. Sarah relance le petit cerceau. Victorino relance le grand. Ils rient du jeu. La marelle bleue reste au sol. Vous jouez ensemble. Bravo. Vous avez des tailles différentes. Et vous jouez ensemble. Sarah saute un carré bleu. Victorino saute le carré d'après. La craie est douce, hein ? Oui. Elle est douce. Le moineau s'envole un peu. Puis il revient. Sarah souffle sur la craie. Un peu de bleu s'envole. Victorino souffle aussi. La poussière brille au soleil. Elle brille. Sarah pose le petit cerceau sur un carré. Victorino pose le grand à côté. Les deux cerceaux se touchent. Petit cerceau. Grand cerceau. Ensemble.</t>
+          <t>La vapeur de la soupe colle à la vitre. Une cuillère en bois attend. Ça sent le thym, tout chaud. Le canapé a trois coussins. Un papillon de nuit tape la lampe. Le tapis est un peu rêche. Tu as vu la buée, Sarah ? Oui. On dirait un nuage. En ce moment, Sarah tire un coussin. Le tissu est doux et lourd. Je veux un train. Jusqu'à la porte. Un train de coussins ? Oui. Pour voir la lune. Sarah pose un coussin. Le tissu fait un petit bruit. Puis un autre. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé. Sarah tend le bras. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Victorino arrive du couloir. Ses chaussettes glissent un peu. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux le train ? Oui. Ils se mettent à quatre pattes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des &lt;emphasis level="moderate"&gt;tailles&lt;/emphasis&gt; différentes. Josette va vers Wilfried. Elle dit : tu veux jouer ? Wilfried dit : oui. Ils jouent ensemble. Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux. Maman dit : petit ou grand, on peut jouer ensemble. Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur de la soupe colle à la vitre. Une cuillère en bois attend. Ça sent le thym, tout chaud. Le canapé a trois coussins. Un papillon de nuit tape la lampe. Le tapis est un peu rêche. Tu as vu la buée, Sarah ? Oui. On dirait un nuage. En ce moment, Sarah tire un coussin. Le tissu est doux et lourd. Je veux un train. Jusqu'à la porte. Un train de coussins ? Oui. Pour voir la lune. Sarah pose un coussin. Le tissu fait un petit bruit. Puis un autre. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé. Sarah tend le bras. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Victorino arrive du couloir. Ses chaussettes glissent un peu. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux le train ? Oui. Ils se mettent à quatre pattes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,69 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La cloche a déjà sonné.
-narrateur|Elle sonne encore, loin.
-narrateur|Les pierres de la cour sont fraîches.
-narrateur|Une marelle bleue attend au sol.
-narrateur|La craie colle un peu aux doigts.
-narrateur|Un moineau saute près du caniveau.
-narrateur|Le foulard de maman bouge au portail.
-narrateur|En ce moment, Sarah est dans la cour.
-maman|Tu vois la marelle, Sarah ?
+          <t>narrateur|La vapeur de la soupe colle à la vitre.
+narrateur|Une cuillère en bois attend.
+narrateur|Ça sent le thym, tout chaud.
+narrateur|Le canapé a trois coussins.
+narrateur|Un papillon de nuit tape la lampe.
+narrateur|Le tapis est un peu rêche.
+maman|Tu as vu la buée, Sarah ?
 enfant-f|Oui.
-enfant-f|Elle est bleue.
-narrateur|Sarah pose le pied sur un carré.
-narrateur|Le carré est un peu poudreux.
-narrateur|Victorino arrive.
-narrateur|Il tient un grand cerceau.
+enfant-f|On dirait un nuage.
+narrateur|En ce moment, Sarah tire un coussin.
+narrateur|Le tissu est doux et lourd.
+enfant-f|Je veux un train.
+enfant-f|Jusqu'à la porte.
+maman|Un train de coussins ?
+enfant-f|Oui.
+enfant-f|Pour voir la lune.
+narrateur|Sarah pose un coussin.
+narrateur|Le tissu fait un petit bruit.
+narrateur|Puis un autre.
+narrateur|Le troisième manque.
+enfant-f|Il est où ?
+maman|Regarde sous la table.
+narrateur|Le coussin est coincé.
+narrateur|Sarah tend le bras.
+narrateur|Ses doigts touchent le tissu.
+narrateur|Le coussin ne vient pas.
+enfant-f|Oh.
+narrateur|Victorino arrive du couloir.
+narrateur|Ses chaussettes glissent un peu.
 narrateur|Victorino est plus grand.
 narrateur|Sarah est plus petite.
 narrateur|Ils ont des tailles différentes.
 maman|Victorino est là.
 maman|Tu l'invites ?
-enfant-f|Tu veux jouer ?
+enfant-f|Tu veux le train ?
 copain|Oui.
-narrateur|Ils jouent ensemble.
-narrateur|Sarah a un petit cerceau.
-narrateur|Victorino a un grand cerceau.
-maman|On joue.
-maman|On reste gentils.
-narrateur|Ils roulent les cerceaux.
-narrateur|Le petit cerceau va vite.
-narrateur|Le grand cerceau va loin.
-narrateur|Les cerceaux font un bruit doux.
-maman|Petit ou grand, on peut jouer ensemble.
-enfant-f|Encore !
-copain|Encore.
-narrateur|Sarah relance le petit cerceau.
-narrateur|Victorino relance le grand.
-narrateur|Ils rient du jeu.
-narrateur|La marelle bleue reste au sol.
-maman|Vous jouez ensemble.
-maman|Bravo.
-maman|Vous avez des tailles différentes.
-maman|Et vous jouez ensemble.
-narrateur|Sarah saute un carré bleu.
-narrateur|Victorino saute le carré d'après.
-maman|La craie est douce, hein ?
-enfant-f|Oui.
-enfant-f|Elle est douce.
-narrateur|Le moineau s'envole un peu.
-narrateur|Puis il revient.
-narrateur|Sarah souffle sur la craie.
-narrateur|Un peu de bleu s'envole.
-narrateur|Victorino souffle aussi.
-maman|La poussière brille au soleil.
-enfant-f|Elle brille.
-narrateur|Sarah pose le petit cerceau sur un carré.
-narrateur|Victorino pose le grand à côté.
-narrateur|Les deux cerceaux se touchent.
-maman|Petit cerceau.
-maman|Grand cerceau.
-maman|Ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Ils se mettent à quatre pattes.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1416,7 +1392,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Josette invite Wilfried. Que font-ils ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah invite Victorino. Que font-ils ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1431,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>jouer ensemble | ensemble | ils jouent | on joue | jouer</t>
+          <t>jouer ensemble | ensemble | ils jouent | on joue | jouer | le train</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1446,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils jouent. Que font Josette et Wilfried ?</t>
+          <t>Ils jouent ensemble. Que font Sarah et Victorino ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1571,7 +1547,6 @@
 narrateur|Que font-ils ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a invité. Victorino a dit oui. Ils ont des tailles différentes. Ils jouent ensemble. Bravo, Sarah. Tu as fait du bon travail. Vous roulez les cerceaux. Sarah tient encore le petit cerceau. Victorino tient le grand. Le mien est petit. Le mien est grand. Et vous jouez ensemble. C'est ça. Ils roulent encore une fois. Les cerceaux s'arrêtent près de la marelle.</t>
+          <t>Victorino soulève un peu la table. Sarah tire le coussin. Le coussin sort, tout chaud. Je l'ai ! Bravo, Sarah. On peut jouer ensemble. Vous jouez ensemble. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part. Le loquet est un peu haut. Victorino tourne le loquet. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Oui. Elle vous attendait.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Josette a invité. Wilfried a dit oui. Ils ont des &lt;emphasis level="moderate"&gt;tailles&lt;/emphasis&gt; différentes. Ils jouent ensemble.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino soulève un peu la table. Sarah tire le coussin. Le coussin sort, tout chaud. Je l'ai ! Bravo, Sarah. On peut jouer ensemble. Vous jouez ensemble. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part. Le loquet est un peu haut. Victorino tourne le loquet. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Oui. Elle vous attendait.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,24 +1715,33 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sarah a invité.
-narrateur|Victorino a dit oui.
-narrateur|Ils ont des tailles différentes.
-narrateur|Ils jouent ensemble.
+          <t>narrateur|Victorino soulève un peu la table.
+narrateur|Sarah tire le coussin.
+narrateur|Le coussin sort, tout chaud.
+enfant-f|Je l'ai !
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
-maman|Vous roulez les cerceaux.
-narrateur|Sarah tient encore le petit cerceau.
-narrateur|Victorino tient le grand.
-enfant-f|Le mien est petit.
-copain|Le mien est grand.
-maman|Et vous jouez ensemble.
-maman|C'est ça.
-narrateur|Ils roulent encore une fois.
-narrateur|Les cerceaux s'arrêtent près de la marelle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+maman|On peut jouer ensemble.
+maman|Vous jouez ensemble.
+narrateur|Ils posent le troisième coussin.
+narrateur|Le train va jusqu'à la porte.
+enfant-f|Tout le monde à bord.
+copain|Moi devant.
+enfant-f|Moi au milieu.
+narrateur|Ils s'assoient sur le tissu.
+narrateur|Le tapis gratte un peu.
+enfant-f|Toc, toc.
+copain|Le train part.
+maman|Le loquet est un peu haut.
+narrateur|Victorino tourne le loquet.
+narrateur|Sarah pousse le dernier coussin.
+narrateur|La porte s'ouvre un peu.
+narrateur|L'air du jardin entre.
+enfant-f|La lune !
+copain|Elle est ronde.
+maman|Oui.
+maman|Elle vous attendait.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1782,12 +1766,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On rentre. Sarah range un cerceau. Victorino range l'autre. Tu as fini de ranger le cerceau ? Oui, maman. Merci. Bravo. Sarah regarde la marelle bleue. La craie brille un peu. Au revoir, marelle. On revient un autre jour. Le foulard de maman bouge encore. Les pierres de la cour restent fraîches.</t>
+          <t>Ils restent sur le dernier coussin. La lune éclaire le seuil. Un peu d'air touche les cheveux. Elle est froide, la lune. On range le train ? Encore un voyage. Un tout petit. Ils reculent d'un coussin. Puis ils avancent encore. Vous avez des tailles différentes. Et vous avez joué ensemble. Tu as fini le voyage ? Oui, maman. Sarah pose un coussin sur le canapé. Victorino pose les deux autres. Merci, Victorino. La vapeur a quitté la vitre. Le thym sent encore un peu.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Maman dit : on rentre. Josette range un cerceau. Wilfried range l'autre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils restent sur le dernier coussin. La lune éclaire le seuil. Un peu d'air touche les cheveux. Elle est froide, la lune. On range le train ? Encore un voyage. Un tout petit. Ils reculent d'un coussin. Puis ils avancent encore. Vous avez des tailles différentes. Et vous avez joué ensemble. Tu as fini le voyage ? Oui, maman. Sarah pose un coussin sur le canapé. Victorino pose les deux autres. Merci, Victorino. La vapeur a quitté la vitre. Le thym sent encore un peu.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1918,22 +1902,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On rentre.
-narrateur|Sarah range un cerceau.
-narrateur|Victorino range l'autre.
-maman|Tu as fini de ranger le cerceau ?
+          <t>narrateur|Ils restent sur le dernier coussin.
+narrateur|La lune éclaire le seuil.
+narrateur|Un peu d'air touche les cheveux.
+enfant-f|Elle est froide, la lune.
+maman|On range le train ?
+enfant-f|Encore un voyage.
+copain|Un tout petit.
+narrateur|Ils reculent d'un coussin.
+narrateur|Puis ils avancent encore.
+maman|Vous avez des tailles différentes.
+maman|Et vous avez joué ensemble.
+maman|Tu as fini le voyage ?
 enfant-f|Oui, maman.
-maman|Merci.
-maman|Bravo.
-narrateur|Sarah regarde la marelle bleue.
-narrateur|La craie brille un peu.
-enfant-f|Au revoir, marelle.
-maman|On revient un autre jour.
-narrateur|Le foulard de maman bouge encore.
-narrateur|Les pierres de la cour restent fraîches.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Sarah pose un coussin sur le canapé.
+narrateur|Victorino pose les deux autres.
+maman|Merci, Victorino.
+narrateur|La vapeur a quitté la vitre.
+narrateur|Le thym sent encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1958,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a joué ensemble. Petit ou grand, on peut jouer ensemble. Bravo. C'était du bon travail. L'histoire est finie.</t>
+          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2026,7 +2014,7 @@
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2098,14 +2086,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On a joué ensemble.
-maman|Petit ou grand, on peut jouer ensemble.
-maman|Bravo.
-maman|C'était du bon travail.
+          <t>enfant-f|On a vu la lune.
+copain|Avec le train.
+maman|Vous avez joué ensemble.
+narrateur|Le thym sent encore un peu.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2124,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2197,6 +2184,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -1946,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu. L'histoire est finie.</t>
+          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu. L'histoire est finie.</t>
+          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2089,8 +2089,7 @@
           <t>enfant-f|On a vu la lune.
 copain|Avec le train.
 maman|Vous avez joué ensemble.
-narrateur|Le thym sent encore un peu.
-narrateur|L'histoire est finie.</t>
+narrateur|Le thym sent encore un peu.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2189,6 +2188,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour de l'école</t>
+          <t>salon puis porte du jardin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Josette, Wilfried, maman</t>
+          <t>Sarah, Victorino, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.COR.001-08.xlsx
+++ b/stories/arbres/ATOM-DIF.COR.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon puis porte du jardin</t>
+          <t>salon puis porte du jardin, vapeur de soupe, cuillère, thym, canapé, coussins</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sarah, Victorino, maman</t>
+          <t>Sarah, Victorino, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sarah veut un train de coussins jusqu'à la porte. Un coussin est coincé. Victorino est plus grand. Sarah est plus petite. Ils vont voir la lune, ensemble.</t>
+          <t>La vapeur colle à la vitre. Une cuillère attend. Ça sent le thym. Sur le tissu, un éclat de coussin brille. Sarah veut un train de coussins jusqu'à la porte, maintenant, pour la lune. Elle tire trop vite, seule : le troisième reste coincé, le train n'atteint pas. Victorino attend, puis soulève. Elle refuse de foncer. Merci vécu. Le loquet est haut. Un éclat de coussin reste pâle.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur de la soupe colle à la vitre. Une cuillère en bois attend. Ça sent le thym, tout chaud. Le canapé a trois coussins. Un papillon de nuit tape la lampe. Le tapis est un peu rêche. Tu as vu la buée, Sarah ? Oui. On dirait un nuage. En ce moment, Sarah tire un coussin. Le tissu est doux et lourd. Je veux un train. Jusqu'à la porte. Un train de coussins ? Oui. Pour voir la lune. Sarah pose un coussin. Le tissu fait un petit bruit. Puis un autre. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé. Sarah tend le bras. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Victorino arrive du couloir. Ses chaussettes glissent un peu. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux le train ? Oui. Ils se mettent à quatre pattes.</t>
+          <t>La vapeur de la soupe colle à la vitre. Elle fait un nuage, un peu flou. On dirait un nuage, papa. Tu l'as vue, Sarah ? Une cuillère en bois attend. Ça sent le thym, près du nez. C'est le thym, dans la soupe. Ça sent bon, maman. Le canapé a trois coussins. Le tapis est un peu rêche. Il gratte, le tapis. Tu as les genoux dessus ? Oui, papa. Un papillon de nuit tape la lampe. La lampe fait un cercle pâle. Il tape, maman. Il cherche la lumière. Sur le tissu, un éclat de coussin brille. Il brille, papa. Tu le vois, sur le tissu ? Oui, il brille. Sarah touche l'éclat de coussin. Le tissu est doux, un peu lourd. Il est doux. Je veux un train, maintenant ! Un train de coussins ? Oui. Jusqu'à la porte. Pour voir le jardin ? Pour voir la lune. En ce moment, Sarah tire un coussin. Elle le pose vers la porte. Le tissu fait un petit bruit. Un autre ! Sarah pose le deuxième, trop vite. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé, sous le bois. Sarah tend le bras, toute seule. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Le train s'arrête, trop court. Il n'atteint pas la porte. Il n'arrive pas ! Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Je le prends ! Sarah tire trop fort, d'un coup. Le tissu reste coincé. Tu le vois, Sarah ? Papa s'accroupit à la même hauteur. Victorino arrive du couloir. Ses chaussettes glissent un peu. Il est plus grand, près de la table. Sarah est plus petite, sous le bois. Tu veux le train ? Victorino ne dit rien, d'abord. Il regarde le coussin, puis Sarah. Oui. Viens. Ils se mettent à quatre pattes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur de la soupe colle à la vitre. Une cuillère en bois attend. Ça sent le thym, tout chaud. Le canapé a trois coussins. Un papillon de nuit tape la lampe. Le tapis est un peu rêche. Tu as vu la buée, Sarah ? Oui. On dirait un nuage. En ce moment, Sarah tire un coussin. Le tissu est doux et lourd. Je veux un train. Jusqu'à la porte. Un train de coussins ? Oui. Pour voir la lune. Sarah pose un coussin. Le tissu fait un petit bruit. Puis un autre. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé. Sarah tend le bras. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Victorino arrive du couloir. Ses chaussettes glissent un peu. Victorino est plus grand. Sarah est plus petite. Ils ont des tailles différentes. Victorino est là. Tu l'invites ? Tu veux le train ? Oui. Ils se mettent à quatre pattes.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vapeur de la soupe colle à la vitre. Elle fait un nuage, un peu flou. On dirait un nuage, papa. Tu l'as vue, Sarah ? Une cuillère en bois attend. Ça sent le thym, près du nez. C'est le thym, dans la soupe. Ça sent bon, maman. Le canapé a trois coussins. Le tapis est un peu rêche. Il gratte, le tapis. Tu as les genoux dessus ? Oui, papa. Un papillon de nuit tape la lampe. La lampe fait un cercle pâle. Il tape, maman. Il cherche la lumière. Sur le tissu, un &lt;emphasis level="moderate"&gt;éclat de coussin&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur le tissu ? Oui, il brille. Sarah touche l'éclat de coussin. Le tissu est doux, un peu lourd. Il est doux. Je veux un train, maintenant ! Un train de coussins ? Oui. Jusqu'à la porte. Pour voir le jardin ? Pour voir la lune. En ce moment, Sarah tire un coussin. Elle le pose vers la porte. Le tissu fait un petit bruit. Un autre ! Sarah pose le deuxième, trop vite. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé, sous le bois. Sarah tend le bras, toute seule. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Le train s'arrête, trop court. Il n'atteint pas la porte. Il n'arrive pas ! Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Je le prends ! Sarah tire trop fort, d'un coup. Le tissu reste coincé. Tu le vois, Sarah ? Papa s'accroupit à la même hauteur. Victorino arrive du couloir. Ses chaussettes glissent un peu. Il est plus grand, près de la table. Sarah est plus petite, sous le bois. Tu veux le train ? Victorino ne dit rien, d'abord. Il regarde le coussin, puis Sarah. Oui. Viens. Ils se mettent à quatre pattes.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Josette est dans la cour. Maman est près du portail. Wilfried arrive. Wilfried est plus grand. Josette est plus petite. Ils ont des &lt;emphasis&gt;tailles&lt;/emphasis&gt; différentes. Josette va vers Wilfried. Elle dit : tu veux jouer ? Wilfried dit : oui. Ils jouent ensemble. Josette a un petit cerceau. Wilfried a un grand cerceau. On ne commente pas le corps. On joue. Ils roulent les cerceaux. Maman dit : petit ou grand, on peut jouer ensemble. Josette rit. Wilfried rit. Ils ont des tailles différentes. Et ils jouent ensemble.&lt;/slow&gt; [pause]</t>
+          <t>La vapeur de la soupe colle à la vitre. Elle fait un nuage, un peu flou. On dirait un nuage, papa. Tu l'as vue, Sarah ? Une cuillère en bois attend. Ça sent le thym, près du nez. C'est le thym, dans la soupe. Ça sent bon, maman. Le canapé a trois coussins. Le tapis est un peu rêche. Il gratte, le tapis. Tu as les genoux dessus ? Oui, papa. Un papillon de nuit tape la lampe. La lampe fait un cercle pâle. Il tape, maman. Il cherche la lumière. Sur le tissu, un &lt;emphasis&gt;éclat de coussin&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur le tissu ? Oui, il brille. Sarah touche l'éclat de coussin. Le tissu est doux, un peu lourd. Il est doux. Je veux un train, maintenant ! Un train de coussins ? Oui. Jusqu'à la porte. Pour voir le jardin ? Pour voir la lune. En ce moment, Sarah tire un coussin. Elle le pose vers la porte. Le tissu fait un petit bruit. Un autre ! Sarah pose le deuxième, trop vite. Le troisième manque. Il est où ? Regarde sous la table. Le coussin est coincé, sous le bois. Sarah tend le bras, toute seule. Ses doigts touchent le tissu. Le coussin ne vient pas. Oh. Le train s'arrête, trop court. Il n'atteint pas la porte. Il n'arrive pas ! Le sourire de Sarah disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Les épaules de Sarah tombent un peu. Ça serre, dans son ventre. Je le prends ! Sarah tire trop fort, d'un coup. Le tissu reste coincé. Tu le vois, Sarah ? Papa s'accroupit à la même hauteur. Victorino arrive du couloir. Ses chaussettes glissent un peu. Il est plus grand, près de la table. Sarah est plus petite, sous le bois. Tu veux le train ? Victorino ne dit rien, d'abord. Il regarde le coussin, puis Sarah. Oui. Viens. Ils se mettent à quatre pattes. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,18 +1241,18 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>tailles</t>
+          <t>éclat de coussin</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1319,48 +1319,85 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience_curieuse puis découragement; intensite=2; destinataire=enfant; sous_texte=elle_veut_le_train_jusqu_a_la_porte_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|La vapeur de la soupe colle à la vitre.
+narrateur|Elle fait un nuage, un peu flou.
+enfant-f|On dirait un nuage, papa.
+papa|Tu l'as vue, Sarah ?
 narrateur|Une cuillère en bois attend.
-narrateur|Ça sent le thym, tout chaud.
+narrateur|Ça sent le thym, près du nez.
+maman|C'est le thym, dans la soupe.
+enfant-f|Ça sent bon, maman.
 narrateur|Le canapé a trois coussins.
+narrateur|Le tapis est un peu rêche.
+enfant-f|Il gratte, le tapis.
+papa|Tu as les genoux dessus ?
+enfant-f|Oui, papa.
 narrateur|Un papillon de nuit tape la lampe.
-narrateur|Le tapis est un peu rêche.
-maman|Tu as vu la buée, Sarah ?
-enfant-f|Oui.
-enfant-f|On dirait un nuage.
-narrateur|En ce moment, Sarah tire un coussin.
-narrateur|Le tissu est doux et lourd.
-enfant-f|Je veux un train.
-enfant-f|Jusqu'à la porte.
+narrateur|La lampe fait un cercle pâle.
+enfant-f|Il tape, maman.
+maman|Il cherche la lumière.
+narrateur|Sur le tissu, un éclat de coussin brille.
+enfant-f|Il brille, papa.
+papa|Tu le vois, sur le tissu ?
+enfant-f|Oui, il brille.
+narrateur|Sarah touche l'éclat de coussin.
+narrateur|Le tissu est doux, un peu lourd.
+enfant-f|Il est doux.
+enfant-f|Je veux un train, maintenant !
 maman|Un train de coussins ?
 enfant-f|Oui.
+enfant-f|Jusqu'à la porte.
+papa|Pour voir le jardin ?
 enfant-f|Pour voir la lune.
-narrateur|Sarah pose un coussin.
+narrateur|En ce moment, Sarah tire un coussin.
+narrateur|Elle le pose vers la porte.
 narrateur|Le tissu fait un petit bruit.
-narrateur|Puis un autre.
+enfant-f|Un autre !
+narrateur|Sarah pose le deuxième, trop vite.
 narrateur|Le troisième manque.
 enfant-f|Il est où ?
 maman|Regarde sous la table.
-narrateur|Le coussin est coincé.
-narrateur|Sarah tend le bras.
+narrateur|Le coussin est coincé, sous le bois.
+narrateur|Sarah tend le bras, toute seule.
 narrateur|Ses doigts touchent le tissu.
 narrateur|Le coussin ne vient pas.
 enfant-f|Oh.
+narrateur|Le train s'arrête, trop court.
+narrateur|Il n'atteint pas la porte.
+enfant-f|Il n'arrive pas !
+narrateur|Le sourire de Sarah disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Les épaules de Sarah tombent un peu.
+narrateur|Ça serre, dans son ventre.
+enfant-f|Je le prends !
+narrateur|Sarah tire trop fort, d'un coup.
+narrateur|Le tissu reste coincé.
+papa|Tu le vois, Sarah ?
+narrateur|Papa s'accroupit à la même hauteur.
 narrateur|Victorino arrive du couloir.
 narrateur|Ses chaussettes glissent un peu.
-narrateur|Victorino est plus grand.
-narrateur|Sarah est plus petite.
-narrateur|Ils ont des tailles différentes.
-maman|Victorino est là.
-maman|Tu l'invites ?
+narrateur|Il est plus grand, près de la table.
+narrateur|Sarah est plus petite, sous le bois.
 enfant-f|Tu veux le train ?
-copain|Oui.
+narrateur|Victorino ne dit rien, d'abord.
+narrateur|Il regarde le coussin, puis Sarah.
+enfant-m|Oui.
+enfant-f|Viens.
 narrateur|Ils se mettent à quatre pattes.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>soupe,coussin</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1429,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Sarah invite Victorino. Que font-ils ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sarah invite &lt;emphasis level="moderate"&gt;Victorino&lt;/emphasis&gt;. Que font-ils ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Josette invite Wilfried. Que font-ils ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Sarah invite &lt;emphasis&gt;Victorino&lt;/emphasis&gt;. Que font-ils ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1460,7 +1497,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1468,10 +1505,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1486,34 +1523,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Victorino</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1522,13 +1563,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1538,7 +1579,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=sarah_invite_ils_tirent_le_coussin_ensemble; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1571,17 +1612,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino soulève un peu la table. Sarah tire le coussin. Le coussin sort, tout chaud. Je l'ai ! Bravo, Sarah. On peut jouer ensemble. Vous jouez ensemble. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part. Le loquet est un peu haut. Victorino tourne le loquet. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Oui. Elle vous attendait.</t>
+          <t>Sarah veut le coussin, toute seule. Je le prends, maintenant ! Elle avance trop vite sous la table. Le tissu reste coincé. Oh. Victorino veut soulever trop haut. Je pousse fort. La table penche un peu. Le coussin recule. Il ne vient pas. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme les mains. Elle écoute le salon, un instant. Tu veux venir près de la table ? Papa reste à la même hauteur. Sarah pose un genou sur le tapis. Le tapis est rêche, un peu. Tu soulèves un peu ? Victorino attend, puis prend le bord. Oui. Il soulève un peu la table. Sarah tire le coussin, tout près. Le coussin sort, un peu plat. Je l'ai ! Oui. Merci, Sarah. Papa a vu les deux, près du bois. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Victorino, tu tiens le bord ? Oui, papa. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino soulève un peu la table. Sarah tire le coussin. Le coussin sort, tout chaud. Je l'ai ! Bravo, Sarah. On peut jouer ensemble. Vous jouez ensemble. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part. Le loquet est un peu haut. Victorino tourne le loquet. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Oui. Elle vous attendait.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah veut le &lt;emphasis level="moderate"&gt;coussin&lt;/emphasis&gt;, toute seule. Je le prends, maintenant ! Elle avance trop vite sous la table. Le tissu reste coincé. Oh. Victorino veut soulever trop haut. Je pousse fort. La table penche un peu. Le coussin recule. Il ne vient pas. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme les mains. Elle écoute le salon, un instant. Tu veux venir près de la table ? Papa reste à la même hauteur. Sarah pose un genou sur le tapis. Le tapis est rêche, un peu. Tu soulèves un peu ? Victorino attend, puis prend le bord. Oui. Il soulève un peu la table. Sarah tire le coussin, tout près. Le coussin sort, un peu plat. Je l'ai ! Oui. Merci, Sarah. Papa a vu les deux, près du bois. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Victorino, tu tiens le bord ? Oui, papa. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Josette a invité. Wilfried a dit oui. Ils ont des &lt;emphasis&gt;tailles&lt;/emphasis&gt; différentes. Ils jouent ensemble.&lt;/slow&gt; [pause]</t>
+          <t>Sarah veut le &lt;emphasis&gt;coussin&lt;/emphasis&gt;, toute seule. Je le prends, maintenant ! Elle avance trop vite sous la table. Le tissu reste coincé. Oh. Victorino veut soulever trop haut. Je pousse fort. La table penche un peu. Le coussin recule. Il ne vient pas. Le sourire ne revient pas. Sarah refuse de foncer. Elle referme les mains. Elle écoute le salon, un instant. Tu veux venir près de la table ? Papa reste à la même hauteur. Sarah pose un genou sur le tapis. Le tapis est rêche, un peu. Tu soulèves un peu ? Victorino attend, puis prend le bord. Oui. Il soulève un peu la table. Sarah tire le coussin, tout près. Le coussin sort, un peu plat. Je l'ai ! Oui. Merci, Sarah. Papa a vu les deux, près du bois. Le ventre de Sarah se desserre. Les épaules se relèvent un peu. Tu as les mains au chaud ? Un peu, maman. Victorino, tu tiens le bord ? Oui, papa. Ils posent le troisième coussin. Le train va jusqu'à la porte. Tout le monde à bord. Moi devant. Moi au milieu. Ils s'assoient sur le tissu. Le tapis gratte un peu. Toc, toc. Le train part. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1628,18 +1669,18 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1662,7 +1703,7 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>tailles</t>
+          <t>coussin</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
@@ -1672,20 +1713,20 @@
         <v>450</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1694,10 +1735,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1706,40 +1747,63 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=confirmation; intention=relancer; emotion=soulagement_prudent; intensite=1; destinataire=enfant; sous_texte=le_tirage_seul_echoue_le_coussin_sort_a_deux; tempo=naturel; sourire=léger; respiration=fluide</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino soulève un peu la table.
-narrateur|Sarah tire le coussin.
-narrateur|Le coussin sort, tout chaud.
+          <t>narrateur|Sarah veut le coussin, toute seule.
+enfant-f|Je le prends, maintenant !
+narrateur|Elle avance trop vite sous la table.
+narrateur|Le tissu reste coincé.
+enfant-f|Oh.
+narrateur|Victorino veut soulever trop haut.
+enfant-m|Je pousse fort.
+narrateur|La table penche un peu.
+narrateur|Le coussin recule.
+enfant-m|Il ne vient pas.
+narrateur|Le sourire ne revient pas.
+narrateur|Sarah refuse de foncer.
+narrateur|Elle referme les mains.
+narrateur|Elle écoute le salon, un instant.
+papa|Tu veux venir près de la table ?
+narrateur|Papa reste à la même hauteur.
+narrateur|Sarah pose un genou sur le tapis.
+narrateur|Le tapis est rêche, un peu.
+enfant-f|Tu soulèves un peu ?
+narrateur|Victorino attend, puis prend le bord.
+enfant-m|Oui.
+narrateur|Il soulève un peu la table.
+narrateur|Sarah tire le coussin, tout près.
+narrateur|Le coussin sort, un peu plat.
 enfant-f|Je l'ai !
-maman|Bravo, Sarah.
-maman|On peut jouer ensemble.
-maman|Vous jouez ensemble.
+enfant-m|Oui.
+papa|Merci, Sarah.
+narrateur|Papa a vu les deux, près du bois.
+narrateur|Le ventre de Sarah se desserre.
+narrateur|Les épaules se relèvent un peu.
+maman|Tu as les mains au chaud ?
+enfant-f|Un peu, maman.
+papa|Victorino, tu tiens le bord ?
+enfant-m|Oui, papa.
 narrateur|Ils posent le troisième coussin.
 narrateur|Le train va jusqu'à la porte.
 enfant-f|Tout le monde à bord.
-copain|Moi devant.
+enfant-m|Moi devant.
 enfant-f|Moi au milieu.
 narrateur|Ils s'assoient sur le tissu.
 narrateur|Le tapis gratte un peu.
 enfant-f|Toc, toc.
-copain|Le train part.
-maman|Le loquet est un peu haut.
-narrateur|Victorino tourne le loquet.
-narrateur|Sarah pousse le dernier coussin.
-narrateur|La porte s'ouvre un peu.
-narrateur|L'air du jardin entre.
-enfant-f|La lune !
-copain|Elle est ronde.
-maman|Oui.
-maman|Elle vous attendait.</t>
+enfant-m|Le train part.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>table,coussin</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1830,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils restent sur le dernier coussin. La lune éclaire le seuil. Un peu d'air touche les cheveux. Elle est froide, la lune. On range le train ? Encore un voyage. Un tout petit. Ils reculent d'un coussin. Puis ils avancent encore. Vous avez des tailles différentes. Et vous avez joué ensemble. Tu as fini le voyage ? Oui, maman. Sarah pose un coussin sur le canapé. Victorino pose les deux autres. Merci, Victorino. La vapeur a quitté la vitre. Le thym sent encore un peu.</t>
+          <t>Sarah veut la porte, d'un coup. J'ouvre, maintenant ! Elle pousse le dernier coussin trop vite. Le train s'arrête avant la porte. Oh. Il manque. Le loquet est un peu haut. Sarah saute vers le loquet. Ses doigts n'arrivent pas. Il est trop haut ! Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Victorino attend, sans parler. Personne ne dit la suite. Sarah observe le tissu, écoute la porte. Sur le tissu, un éclat de coussin luit. Là, sur le tissu. Sarah tient le coussin des deux mains. Tu tournes le loquet ? Oui. Victorino tourne le loquet, plus haut. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Tu la vois, Sarah ? Oui, papa. On avance ? Oui, maman. Un peu d'air touche les cheveux. Elle est froide, la lune. On reste un moment. Ils restent sur le dernier coussin. La lune éclaire le seuil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ils restent sur le dernier coussin. La lune éclaire le seuil. Un peu d'air touche les cheveux. Elle est froide, la lune. On range le train ? Encore un voyage. Un tout petit. Ils reculent d'un coussin. Puis ils avancent encore. Vous avez des tailles différentes. Et vous avez joué ensemble. Tu as fini le voyage ? Oui, maman. Sarah pose un coussin sur le canapé. Victorino pose les deux autres. Merci, Victorino. La vapeur a quitté la vitre. Le thym sent encore un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sarah veut la porte, d'un coup. J'ouvre, maintenant ! Elle pousse le dernier coussin trop vite. Le train s'arrête avant la porte. Oh. Il manque. Le loquet est un peu haut. Sarah saute vers le loquet. Ses doigts n'arrivent pas. Il est trop haut ! Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Victorino attend, sans parler. Personne ne dit la suite. Sarah observe le tissu, écoute la porte. Sur le tissu, un &lt;emphasis level="moderate"&gt;éclat de coussin&lt;/emphasis&gt; luit. Là, sur le tissu. Sarah tient le coussin des deux mains. Tu tournes le loquet ? Oui. Victorino tourne le loquet, plus haut. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Tu la vois, Sarah ? Oui, papa. On avance ? Oui, maman. Un peu d'air touche les cheveux. Elle est froide, la lune. On reste un moment. Ils restent sur le dernier coussin. La lune éclaire le seuil.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Maman dit : on rentre. Josette range un cerceau. Wilfried range l'autre.&lt;/slow&gt; [pause]</t>
+          <t>Sarah veut la porte, d'un coup. J'ouvre, maintenant ! Elle pousse le dernier coussin trop vite. Le train s'arrête avant la porte. Oh. Il manque. Le loquet est un peu haut. Sarah saute vers le loquet. Ses doigts n'arrivent pas. Il est trop haut ! Sarah avance les mains. Puis elle s'arrête net. Attends, je regarde. Victorino attend, sans parler. Personne ne dit la suite. Sarah observe le tissu, écoute la porte. Sur le tissu, un &lt;emphasis&gt;éclat de coussin&lt;/emphasis&gt; luit. Là, sur le tissu. Sarah tient le coussin des deux mains. Tu tournes le loquet ? Oui. Victorino tourne le loquet, plus haut. Sarah pousse le dernier coussin. La porte s'ouvre un peu. L'air du jardin entre. La lune ! Elle est ronde. Tu la vois, Sarah ? Oui, papa. On avance ? Oui, maman. Un peu d'air touche les cheveux. Elle est froide, la lune. On reste un moment. Ils restent sur le dernier coussin. La lune éclaire le seuil. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1823,18 +1887,18 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1855,28 +1919,32 @@
       <c r="AG5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>éclat de coussin</t>
+        </is>
+      </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1885,10 +1953,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1897,29 +1965,56 @@
         <v>50</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=elle_refuse_de_foncer_sans_regarder_l_eclat; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils restent sur le dernier coussin.
-narrateur|La lune éclaire le seuil.
+          <t>narrateur|Sarah veut la porte, d'un coup.
+enfant-f|J'ouvre, maintenant !
+narrateur|Elle pousse le dernier coussin trop vite.
+narrateur|Le train s'arrête avant la porte.
+enfant-f|Oh.
+enfant-m|Il manque.
+narrateur|Le loquet est un peu haut.
+narrateur|Sarah saute vers le loquet.
+narrateur|Ses doigts n'arrivent pas.
+enfant-f|Il est trop haut !
+narrateur|Sarah avance les mains.
+narrateur|Puis elle s'arrête net.
+enfant-f|Attends, je regarde.
+narrateur|Victorino attend, sans parler.
+narrateur|Personne ne dit la suite.
+narrateur|Sarah observe le tissu, écoute la porte.
+narrateur|Sur le tissu, un éclat de coussin luit.
+enfant-f|Là, sur le tissu.
+narrateur|Sarah tient le coussin des deux mains.
+enfant-f|Tu tournes le loquet ?
+enfant-m|Oui.
+narrateur|Victorino tourne le loquet, plus haut.
+narrateur|Sarah pousse le dernier coussin.
+narrateur|La porte s'ouvre un peu.
+narrateur|L'air du jardin entre.
+enfant-f|La lune !
+enfant-m|Elle est ronde.
+papa|Tu la vois, Sarah ?
+enfant-f|Oui, papa.
+maman|On avance ?
+enfant-f|Oui, maman.
 narrateur|Un peu d'air touche les cheveux.
 enfant-f|Elle est froide, la lune.
-maman|On range le train ?
-enfant-f|Encore un voyage.
-copain|Un tout petit.
-narrateur|Ils reculent d'un coussin.
-narrateur|Puis ils avancent encore.
-maman|Vous avez des tailles différentes.
-maman|Et vous avez joué ensemble.
-maman|Tu as fini le voyage ?
-enfant-f|Oui, maman.
-narrateur|Sarah pose un coussin sur le canapé.
-narrateur|Victorino pose les deux autres.
-maman|Merci, Victorino.
-narrateur|La vapeur a quitté la vitre.
-narrateur|Le thym sent encore un peu.</t>
+papa|On reste un moment.
+narrateur|Ils restent sur le dernier coussin.
+narrateur|La lune éclaire le seuil.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>porte,jardin</t>
         </is>
       </c>
     </row>
@@ -1946,17 +2041,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu.</t>
+          <t>La vitre brillait, papa. Tu la vois, comme sur le tissu ? Oui, dans la vapeur. Sarah pose un coussin sur le canapé. On le remet ? Oui, maman. Le thym sentait bon. Il est derrière nous. La vapeur a quitté la vitre. Sarah respire, plus large. On rentre ? Oui. À demain. À demain. Les joues de Sarah se réchauffent. Victorino pose les deux autres. Un éclat de coussin reste pâle.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a vu la lune. Avec le train. Vous avez joué ensemble. Le thym sent encore un peu.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La vitre brillait, papa. Tu la vois, comme sur le tissu ? Oui, dans la vapeur. Sarah pose un coussin sur le canapé. On le remet ? Oui, maman. Le thym sentait bon. Il est derrière nous. La vapeur a quitté la vitre. Sarah respire, plus large. On rentre ? Oui. À demain. À demain. Les joues de Sarah se réchauffent. Victorino pose les deux autres. Un &lt;emphasis level="moderate"&gt;éclat de coussin&lt;/emphasis&gt; reste pâle.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La vitre brillait, papa. Tu la vois, comme sur le tissu ? Oui, dans la vapeur. Sarah pose un coussin sur le canapé. On le remet ? Oui, maman. Le thym sentait bon. Il est derrière nous. La vapeur a quitté la vitre. Sarah respire, plus large. On rentre ? Oui. À demain. À demain. Les joues de Sarah se réchauffent. Victorino pose les deux autres. Un &lt;emphasis&gt;éclat de coussin&lt;/emphasis&gt; reste pâle.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2003,7 +2098,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2011,7 +2106,7 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1.28</v>
@@ -2023,12 +2118,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2037,17 +2132,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de coussin</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2056,11 +2155,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2069,27 +2168,49 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_pale; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|On a vu la lune.
-copain|Avec le train.
-maman|Vous avez joué ensemble.
-narrateur|Le thym sent encore un peu.</t>
+          <t>enfant-f|La vitre brillait, papa.
+papa|Tu la vois, comme sur le tissu ?
+enfant-f|Oui, dans la vapeur.
+narrateur|Sarah pose un coussin sur le canapé.
+maman|On le remet ?
+enfant-f|Oui, maman.
+enfant-f|Le thym sentait bon.
+maman|Il est derrière nous.
+narrateur|La vapeur a quitté la vitre.
+narrateur|Sarah respire, plus large.
+papa|On rentre ?
+enfant-f|Oui.
+enfant-m|À demain.
+enfant-f|À demain.
+narrateur|Les joues de Sarah se réchauffent.
+narrateur|Victorino pose les deux autres.
+narrateur|Un éclat de coussin reste pâle.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>vapeur</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2316,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
